--- a/Data/Processed/Sensitivity/PGLS/coef_prop_threat_pgls.xlsx
+++ b/Data/Processed/Sensitivity/PGLS/coef_prop_threat_pgls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\OneDrive\Desktop\Collabs\Extinction_dynamics_Iberic\Data\Processed\Sensitivity\PGLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D4DA65-3905-4A20-B8FC-ECBEC8739696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00C27BD-34B0-48EE-9460-143DEBDB9592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,9 +82,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
       <t>2</t>
     </r>
@@ -95,10 +94,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,12 +115,24 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -144,31 +155,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
@@ -483,31 +498,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -518,75 +533,75 @@
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <v>0.1566988830582671</v>
       </c>
       <c r="E2" s="6">
         <v>2.5134807318648492E-2</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>6.2343379470431071</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="9">
         <v>0</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <v>1.0333213591630501E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>2.8944996796070252E-3</v>
       </c>
       <c r="E3" s="6">
         <v>3.1980426558218698E-3</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="7">
         <v>0.90508476312463804</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="10">
         <v>0.36566848750551778</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="9">
         <v>0</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="5">
         <v>1.0333213591630501E-2</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>-9.6063290098720389E-2</v>
       </c>
       <c r="E4" s="6">
         <v>5.2655415297687351E-2</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>-1.8243762689103611</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="10">
         <v>6.8434558392860723E-2</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="9">
         <v>0</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>1.0333213591630501E-2</v>
       </c>
     </row>
@@ -595,75 +610,75 @@
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>0.162388798906409</v>
       </c>
       <c r="E5" s="6">
         <v>1.950200877918459E-2</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>8.3267729363210119</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="9">
         <v>0</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <v>1.035222513103063E-2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>1.3976982414150561E-3</v>
       </c>
       <c r="E6" s="6">
         <v>1.528584570033781E-3</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>0.91437416601959254</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="10">
         <v>0.36077102024510621</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="9">
         <v>0</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <v>1.035222513103063E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>-0.1020995736623465</v>
       </c>
       <c r="E7" s="6">
         <v>4.8955869362602843E-2</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>-2.0855430613666082</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="10">
         <v>3.7307963513709907E-2</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="9">
         <v>0</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="5">
         <v>1.035222513103063E-2</v>
       </c>
     </row>
@@ -672,75 +687,75 @@
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>0.16617251851898271</v>
       </c>
       <c r="E8" s="6">
         <v>1.536104481746481E-2</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>10.81778749385928</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="9">
         <v>0</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="5">
         <v>1.0563679839229361E-2</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>7.2605051844892485E-4</v>
       </c>
       <c r="E9" s="6">
         <v>7.1745246585528169E-4</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>1.0119841425081639</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="10">
         <v>0.311824114092903</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="9">
         <v>0</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="5">
         <v>1.0563679839229361E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>-0.1066415724825539</v>
       </c>
       <c r="E10" s="6">
         <v>4.6049586203897479E-2</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>-2.3157987133775402</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="10">
         <v>2.079858636653031E-2</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <v>0</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="5">
         <v>1.0563679839229361E-2</v>
       </c>
     </row>
@@ -751,75 +766,75 @@
       <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <v>0.21167907801064531</v>
       </c>
       <c r="E11" s="6">
         <v>9.4220172555574341E-2</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>2.246642860750331</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="10">
         <v>2.4967224918690519E-2</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="5">
         <v>0.29879119514489533</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="5">
         <v>6.5468236756326464E-3</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>7.6893185372108874E-3</v>
       </c>
       <c r="E12" s="6">
         <v>4.1503070698654899E-3</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>1.8527107531491871</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="10">
         <v>6.4335710950443215E-2</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="5">
         <v>0.29879119514489533</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="5">
         <v>6.5468236756326464E-3</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>-1.340747963914333E-2</v>
       </c>
       <c r="E13" s="6">
         <v>5.8502975203892263E-2</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>-0.2291760306619639</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="10">
         <v>0.81879763916281356</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="5">
         <v>0.29879119514489533</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="5">
         <v>6.5468236756326464E-3</v>
       </c>
     </row>
@@ -828,75 +843,75 @@
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>0.2121641708189036</v>
       </c>
       <c r="E14" s="6">
         <v>9.0974467411458246E-2</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>2.3321287483809048</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="10">
         <v>1.9970656271434791E-2</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="5">
         <v>0.28259222043752968</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <v>6.9512963310816283E-3</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>3.9444480388312296E-3</v>
       </c>
       <c r="E15" s="6">
         <v>2.0598007850277421E-3</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>1.9149657906252839</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="10">
         <v>5.5895576548367742E-2</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="5">
         <v>0.28259222043752968</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>6.9512963310816283E-3</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>-2.561145162294105E-2</v>
       </c>
       <c r="E16" s="6">
         <v>5.5907770962049623E-2</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>-0.45810181987627779</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="10">
         <v>0.64701848201091461</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="5">
         <v>0.28259222043752968</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>6.9512963310816283E-3</v>
       </c>
     </row>
@@ -905,77 +920,88 @@
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>0.1123715599249711</v>
       </c>
       <c r="E17" s="6">
         <v>1.7176193267997061E-2</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>6.5422854861759978</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="9">
         <v>0</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="5">
         <v>2.6424758251378959E-2</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="5">
         <v>2.8901153690890058E-3</v>
       </c>
       <c r="E18" s="6">
         <v>8.329505914814227E-4</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>3.4697320569145238</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="9">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="5">
         <v>2.6424758251378959E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="5">
         <v>-6.0490561338805947E-2</v>
       </c>
       <c r="E19" s="6">
         <v>4.8969670120778228E-2</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <v>-1.235265853121182</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="10">
         <v>0.217137313622245</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="9">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="5">
         <v>2.6424758251378959E-2</v>
       </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -989,5 +1015,6 @@
     <mergeCell ref="B17:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>